--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.92530492683</v>
+        <v>46157.93101658432</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93101658432</v>
+        <v>46157.93360095936</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93360095936</v>
+        <v>46157.93658088338</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93658088338</v>
+        <v>46158.28187120035</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.29780354022</v>
+        <v>46158.33347577918</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.33347577918</v>
+        <v>46158.37205481853</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.37205481853</v>
+        <v>46158.37407543881</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">
